--- a/artfynd/A 6680-2026 artfynd.xlsx
+++ b/artfynd/A 6680-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40459</v>
+        <v>119993601</v>
       </c>
       <c r="B2" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,24 +710,29 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västansjö, Mpd</t>
+          <t>Kovlebodarn, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592319.4610503789</v>
+        <v>592433</v>
       </c>
       <c r="R2" t="n">
-        <v>6930829.100794828</v>
+        <v>6930850</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,27 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-05-18</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-05-18</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på skogsbilväg</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,49 +789,48 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oskar Norrgrann, Frans Olofsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119993601</v>
+        <v>40459</v>
       </c>
       <c r="B3" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100053</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,29 +840,24 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kovlebodarn, Mpd</t>
+          <t>Västansjö, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592433</v>
+        <v>592319</v>
       </c>
       <c r="R3" t="n">
-        <v>6930850</v>
+        <v>6930829</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -895,22 +884,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2011-05-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2011-05-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på skogsbilväg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,19 +909,15 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Nilsson</t>
+          <t>Oskar Norrgrann</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Oskar Norrgrann, Frans Olofsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
